--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7593" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7593" uniqueCount="566">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -854,6 +854,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Procedure.statusCode</t>
@@ -8575,7 +8579,7 @@
         <v>74</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>74</v>
@@ -8583,10 +8587,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8612,10 +8616,10 @@
         <v>91</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8646,7 +8650,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -8664,7 +8668,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8684,10 +8688,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8710,13 +8714,13 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8767,7 +8771,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8787,10 +8791,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8813,13 +8817,13 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8850,7 +8854,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8868,7 +8872,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8888,10 +8892,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8947,25 +8951,25 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8985,10 +8989,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9011,11 +9015,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9066,7 +9070,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9086,10 +9090,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9115,10 +9119,10 @@
         <v>181</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9169,7 +9173,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -9189,10 +9193,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9290,10 +9294,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9393,10 +9397,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9496,10 +9500,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9599,10 +9603,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9702,10 +9706,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9805,10 +9809,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9906,10 +9910,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10007,10 +10011,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10110,10 +10114,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10141,10 +10145,10 @@
         <v>219</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10215,10 +10219,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10318,10 +10322,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10347,10 +10351,10 @@
         <v>181</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10401,7 +10405,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10421,10 +10425,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10522,10 +10526,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10625,10 +10629,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10728,10 +10732,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10831,10 +10835,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10934,10 +10938,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11037,10 +11041,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11138,10 +11142,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11239,10 +11243,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11342,10 +11346,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11373,10 +11377,10 @@
         <v>219</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11447,10 +11451,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11548,17 +11552,17 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>80</v>
@@ -11576,11 +11580,11 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11631,7 +11635,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11651,10 +11655,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11679,11 +11683,11 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11734,7 +11738,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11754,10 +11758,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11855,10 +11859,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11899,7 +11903,7 @@
         <v>74</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>74</v>
@@ -11958,10 +11962,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12002,7 +12006,7 @@
         <v>74</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>74</v>
@@ -12061,10 +12065,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12105,7 +12109,7 @@
         <v>74</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>74</v>
@@ -12164,10 +12168,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12267,10 +12271,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12311,7 +12315,7 @@
         <v>74</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>74</v>
@@ -12370,10 +12374,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12471,10 +12475,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12572,10 +12576,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12675,10 +12679,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12778,10 +12782,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12881,10 +12885,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12912,10 +12916,10 @@
         <v>181</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12966,7 +12970,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12986,10 +12990,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13089,10 +13093,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13115,7 +13119,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -13168,7 +13172,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -13188,10 +13192,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13214,7 +13218,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -13267,7 +13271,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -13287,10 +13291,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13313,7 +13317,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -13366,7 +13370,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13386,10 +13390,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13412,7 +13416,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13465,7 +13469,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13485,10 +13489,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13511,7 +13515,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13564,7 +13568,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13584,10 +13588,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13610,7 +13614,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13663,7 +13667,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13683,10 +13687,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13709,7 +13713,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13750,7 +13754,7 @@
         <v>74</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AC114" s="2"/>
       <c r="AD114" t="s" s="2">
@@ -13760,7 +13764,7 @@
         <v>125</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13780,13 +13784,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>74</v>
@@ -13808,13 +13812,13 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13865,7 +13869,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13885,10 +13889,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13986,10 +13990,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14087,10 +14091,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14188,10 +14192,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14289,10 +14293,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14392,10 +14396,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14495,10 +14499,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14598,10 +14602,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14701,10 +14705,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14802,10 +14806,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14842,7 +14846,7 @@
         <v>74</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>74</v>
@@ -14861,7 +14865,7 @@
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>74</v>
@@ -14879,7 +14883,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -14899,10 +14903,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14929,7 +14933,7 @@
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14941,7 +14945,7 @@
         <v>74</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>74</v>
@@ -14980,7 +14984,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -15000,10 +15004,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15030,12 +15034,12 @@
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
@@ -15081,7 +15085,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -15101,10 +15105,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15180,7 +15184,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -15200,10 +15204,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15226,7 +15230,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -15279,7 +15283,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -15299,10 +15303,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15325,7 +15329,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15378,7 +15382,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -15398,10 +15402,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15424,7 +15428,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15477,7 +15481,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15497,10 +15501,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15523,7 +15527,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15576,7 +15580,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15596,10 +15600,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15622,7 +15626,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15675,7 +15679,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15695,10 +15699,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15721,7 +15725,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15774,7 +15778,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15794,10 +15798,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15820,7 +15824,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15873,7 +15877,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15893,10 +15897,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15919,7 +15923,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15972,7 +15976,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15992,10 +15996,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16018,7 +16022,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -16071,7 +16075,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -16091,10 +16095,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16117,7 +16121,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -16170,7 +16174,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -16190,10 +16194,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16216,7 +16220,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16269,7 +16273,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -16289,13 +16293,13 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>74</v>
@@ -16317,13 +16321,13 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -16374,7 +16378,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16394,10 +16398,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16495,10 +16499,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16596,10 +16600,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16697,10 +16701,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16798,10 +16802,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16901,10 +16905,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17004,10 +17008,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17107,10 +17111,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17210,10 +17214,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17311,10 +17315,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17351,7 +17355,7 @@
         <v>74</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>74</v>
@@ -17370,7 +17374,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>74</v>
@@ -17388,7 +17392,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>75</v>
@@ -17408,10 +17412,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17438,7 +17442,7 @@
       </c>
       <c r="L151" s="2"/>
       <c r="M151" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17489,7 +17493,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17509,10 +17513,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17539,12 +17543,12 @@
       </c>
       <c r="L152" s="2"/>
       <c r="M152" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
@@ -17590,7 +17594,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17610,10 +17614,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17689,7 +17693,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17709,10 +17713,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17735,7 +17739,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17788,7 +17792,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17808,10 +17812,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17834,7 +17838,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17887,7 +17891,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17907,10 +17911,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17933,7 +17937,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17986,7 +17990,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -18006,10 +18010,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18032,7 +18036,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -18085,7 +18089,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -18105,10 +18109,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18131,7 +18135,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -18184,7 +18188,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -18204,10 +18208,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18230,7 +18234,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -18283,7 +18287,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -18303,10 +18307,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18329,7 +18333,7 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -18382,7 +18386,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18402,10 +18406,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18428,7 +18432,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18481,7 +18485,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18501,10 +18505,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18527,7 +18531,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18580,7 +18584,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18600,10 +18604,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18626,7 +18630,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18679,7 +18683,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18699,10 +18703,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18725,7 +18729,7 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18778,7 +18782,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18798,13 +18802,13 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>74</v>
@@ -18826,13 +18830,13 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -18883,7 +18887,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18903,10 +18907,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19004,10 +19008,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19105,10 +19109,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19206,10 +19210,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19307,10 +19311,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19410,10 +19414,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19513,10 +19517,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19616,10 +19620,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19719,10 +19723,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19820,10 +19824,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19860,7 +19864,7 @@
         <v>74</v>
       </c>
       <c r="S175" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="T175" t="s" s="2">
         <v>74</v>
@@ -19879,7 +19883,7 @@
       </c>
       <c r="Y175" s="2"/>
       <c r="Z175" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>74</v>
@@ -19897,7 +19901,7 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>75</v>
@@ -19917,10 +19921,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19947,7 +19951,7 @@
       </c>
       <c r="L176" s="2"/>
       <c r="M176" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -19998,7 +20002,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -20018,10 +20022,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20048,12 +20052,12 @@
       </c>
       <c r="L177" s="2"/>
       <c r="M177" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
@@ -20099,7 +20103,7 @@
         <v>74</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -20119,10 +20123,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20198,7 +20202,7 @@
         <v>74</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -20218,10 +20222,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20244,7 +20248,7 @@
         <v>74</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20297,7 +20301,7 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -20317,10 +20321,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20343,7 +20347,7 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
@@ -20396,7 +20400,7 @@
         <v>74</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -20416,10 +20420,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20442,7 +20446,7 @@
         <v>74</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
@@ -20495,7 +20499,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -20515,10 +20519,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20541,7 +20545,7 @@
         <v>74</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
@@ -20594,7 +20598,7 @@
         <v>74</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -20614,10 +20618,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20640,7 +20644,7 @@
         <v>74</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
@@ -20693,7 +20697,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -20713,10 +20717,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20739,7 +20743,7 @@
         <v>74</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
@@ -20792,7 +20796,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -20812,10 +20816,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20838,7 +20842,7 @@
         <v>74</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -20891,7 +20895,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -20911,10 +20915,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20937,7 +20941,7 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -20990,7 +20994,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -21010,10 +21014,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21036,7 +21040,7 @@
         <v>74</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -21089,7 +21093,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -21109,10 +21113,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21135,7 +21139,7 @@
         <v>74</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
@@ -21188,7 +21192,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -21208,10 +21212,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21234,7 +21238,7 @@
         <v>74</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21287,7 +21291,7 @@
         <v>74</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -21307,13 +21311,13 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D190" t="s" s="2">
         <v>74</v>
@@ -21335,13 +21339,13 @@
         <v>74</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -21392,7 +21396,7 @@
         <v>74</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -21412,10 +21416,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21513,10 +21517,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21614,10 +21618,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21715,10 +21719,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21816,10 +21820,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21919,10 +21923,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22022,10 +22026,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22125,10 +22129,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22228,10 +22232,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22329,10 +22333,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22369,7 +22373,7 @@
         <v>74</v>
       </c>
       <c r="S200" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T200" t="s" s="2">
         <v>74</v>
@@ -22388,7 +22392,7 @@
       </c>
       <c r="Y200" s="2"/>
       <c r="Z200" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>74</v>
@@ -22406,7 +22410,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>75</v>
@@ -22426,10 +22430,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22456,7 +22460,7 @@
       </c>
       <c r="L201" s="2"/>
       <c r="M201" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -22507,7 +22511,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -22527,10 +22531,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22557,12 +22561,12 @@
       </c>
       <c r="L202" s="2"/>
       <c r="M202" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q202" s="2"/>
       <c r="R202" t="s" s="2">
@@ -22608,7 +22612,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -22628,10 +22632,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22707,7 +22711,7 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -22727,10 +22731,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22753,7 +22757,7 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -22806,7 +22810,7 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -22826,10 +22830,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22852,7 +22856,7 @@
         <v>74</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -22905,7 +22909,7 @@
         <v>74</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -22925,10 +22929,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -22951,7 +22955,7 @@
         <v>74</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
@@ -23004,7 +23008,7 @@
         <v>74</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -23024,10 +23028,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23050,7 +23054,7 @@
         <v>74</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
@@ -23103,7 +23107,7 @@
         <v>74</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -23123,10 +23127,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23149,7 +23153,7 @@
         <v>74</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
@@ -23202,7 +23206,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -23222,10 +23226,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23248,7 +23252,7 @@
         <v>74</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
@@ -23301,7 +23305,7 @@
         <v>74</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -23321,10 +23325,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23347,7 +23351,7 @@
         <v>74</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
@@ -23400,7 +23404,7 @@
         <v>74</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -23420,10 +23424,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23446,7 +23450,7 @@
         <v>74</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23499,7 +23503,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -23519,10 +23523,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23545,7 +23549,7 @@
         <v>74</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23598,7 +23602,7 @@
         <v>74</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -23618,10 +23622,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23644,7 +23648,7 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -23697,7 +23701,7 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -23717,10 +23721,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23743,7 +23747,7 @@
         <v>74</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23796,7 +23800,7 @@
         <v>74</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -23816,13 +23820,13 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D215" t="s" s="2">
         <v>74</v>
@@ -23844,13 +23848,13 @@
         <v>74</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -23901,7 +23905,7 @@
         <v>74</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -23921,10 +23925,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24022,10 +24026,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24123,10 +24127,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24224,10 +24228,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24325,10 +24329,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24428,10 +24432,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24531,10 +24535,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24634,10 +24638,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24737,10 +24741,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24838,10 +24842,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -24878,7 +24882,7 @@
         <v>74</v>
       </c>
       <c r="S225" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T225" t="s" s="2">
         <v>74</v>
@@ -24897,7 +24901,7 @@
       </c>
       <c r="Y225" s="2"/>
       <c r="Z225" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>74</v>
@@ -24915,7 +24919,7 @@
         <v>74</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>75</v>
@@ -24935,10 +24939,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -24965,7 +24969,7 @@
       </c>
       <c r="L226" s="2"/>
       <c r="M226" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -25016,7 +25020,7 @@
         <v>74</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
@@ -25036,10 +25040,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25066,12 +25070,12 @@
       </c>
       <c r="L227" s="2"/>
       <c r="M227" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" t="s" s="2">
@@ -25117,7 +25121,7 @@
         <v>74</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -25137,10 +25141,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25216,7 +25220,7 @@
         <v>74</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
@@ -25236,10 +25240,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25262,7 +25266,7 @@
         <v>74</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -25315,7 +25319,7 @@
         <v>74</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
@@ -25335,10 +25339,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25361,7 +25365,7 @@
         <v>74</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
@@ -25414,7 +25418,7 @@
         <v>74</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>80</v>
@@ -25434,10 +25438,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25460,7 +25464,7 @@
         <v>74</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
@@ -25513,7 +25517,7 @@
         <v>74</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -25533,10 +25537,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25559,7 +25563,7 @@
         <v>74</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
@@ -25612,7 +25616,7 @@
         <v>74</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
@@ -25632,10 +25636,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25658,7 +25662,7 @@
         <v>74</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
@@ -25711,7 +25715,7 @@
         <v>74</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>80</v>
@@ -25731,10 +25735,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25757,7 +25761,7 @@
         <v>74</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -25810,7 +25814,7 @@
         <v>74</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
@@ -25830,10 +25834,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -25856,7 +25860,7 @@
         <v>74</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
@@ -25909,7 +25913,7 @@
         <v>74</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>80</v>
@@ -25929,10 +25933,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -25955,7 +25959,7 @@
         <v>74</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
@@ -26008,7 +26012,7 @@
         <v>74</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
@@ -26028,10 +26032,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26054,7 +26058,7 @@
         <v>74</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
@@ -26107,7 +26111,7 @@
         <v>74</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>80</v>
@@ -26127,10 +26131,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26153,7 +26157,7 @@
         <v>74</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
@@ -26206,7 +26210,7 @@
         <v>74</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>80</v>
@@ -26226,10 +26230,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26252,7 +26256,7 @@
         <v>74</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
@@ -26305,7 +26309,7 @@
         <v>74</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>80</v>
@@ -26325,10 +26329,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26351,7 +26355,7 @@
         <v>74</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
@@ -26404,7 +26408,7 @@
         <v>74</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>80</v>
@@ -26424,10 +26428,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26450,7 +26454,7 @@
         <v>74</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L241" s="2"/>
       <c r="M241" s="2"/>
@@ -26503,7 +26507,7 @@
         <v>74</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>80</v>
@@ -26523,10 +26527,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26549,7 +26553,7 @@
         <v>74</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L242" s="2"/>
       <c r="M242" s="2"/>
@@ -26602,7 +26606,7 @@
         <v>74</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>80</v>
@@ -26622,10 +26626,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -26648,7 +26652,7 @@
         <v>74</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
@@ -26701,7 +26705,7 @@
         <v>74</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
